--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9190</v>
+        <v>9144</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13694</v>
+        <v>13844</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4504</v>
+        <v>-4700</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -587,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9468</v>
+        <v>9328</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13694</v>
+        <v>13844</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4226</v>
+        <v>-4516</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9468</v>
+        <v>9328</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13694</v>
+        <v>13844</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4226</v>
+        <v>-4516</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>9524</v>
+        <v>8535</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13694</v>
+        <v>13844</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4170</v>
+        <v>-5309</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -722,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8436</v>
+        <v>8811</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16162</v>
+        <v>13844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-7726</v>
+        <v>-5033</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -767,30 +767,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8764</v>
+        <v>8847</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16162</v>
+        <v>13844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-7398</v>
+        <v>-4997</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>9190</v>
+        <v>8535</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16162</v>
+        <v>14849</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6972</v>
+        <v>-6314</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>9022</v>
+        <v>8847</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14684</v>
+        <v>14849</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5662</v>
+        <v>-6002</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9022</v>
+        <v>8847</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14684</v>
+        <v>14849</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5662</v>
+        <v>-6002</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9078</v>
+        <v>7011</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>14684</v>
+        <v>12853</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5606</v>
+        <v>-5842</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9190</v>
+        <v>7148</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>14684</v>
+        <v>12853</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5494</v>
+        <v>-5705</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1013,9 +1013,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1037,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6711</v>
+        <v>7177</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13694</v>
+        <v>12853</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-6983</v>
+        <v>-5676</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7042</v>
+        <v>9144</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>13694</v>
+        <v>12853</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-6652</v>
+        <v>-3709</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>30</v>
@@ -1103,9 +1103,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9190</v>
+        <v>9187</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>13694</v>
+        <v>12853</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4504</v>
+        <v>-3666</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1172,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9022</v>
+        <v>9328</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12704</v>
+        <v>12853</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3682</v>
+        <v>-3525</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1199,636 +1199,6 @@
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>14-JUN-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-115</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>9190</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>12704</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-3514</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>14-JUN-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>9524</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>12704</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-3180</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>24-JUN-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-140</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>7042</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>10724</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-3682</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>06-SEP-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>06-SEP-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-115</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>13959</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-2203</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>13-SEP-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>13-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-115</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>9385</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-6777</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>20-SEP-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-591</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>8685</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-7477</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>20-SEP-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>20-SEP-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-115</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>8994</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>16162</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-7168</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,9 +80,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9144</v>
+        <v>9328</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>13844</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4700</v>
+        <v>-4516</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -587,7 +578,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -632,17 +623,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9328</v>
+        <v>9583</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>13844</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4516</v>
+        <v>-4261</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -677,26 +668,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8535</v>
+        <v>8657</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>13844</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5309</v>
+        <v>-5187</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -722,26 +713,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8811</v>
+        <v>8847</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>13844</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5033</v>
+        <v>-4997</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -767,17 +758,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8847</v>
+        <v>9144</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>13844</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4997</v>
+        <v>-4700</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -794,411 +785,6 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-140</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>8535</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>14849</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-6314</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>14849</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-6002</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-115</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>8847</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>14849</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-6002</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-591</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>7011</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>12853</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-5842</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-140</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>7148</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>12853</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-5705</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>7177</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>12853</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-5676</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>14-JUN-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-142</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>9144</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>12853</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-3709</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>14-JUN-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-115</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>9187</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>12853</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-3666</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>14-JUN-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>9328</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>12853</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-3525</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -533,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9328</v>
+        <v>9117</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13844</v>
+        <v>13824</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4516</v>
+        <v>-4707</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -578,17 +587,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9328</v>
+        <v>9287</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13844</v>
+        <v>13824</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4516</v>
+        <v>-4537</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -623,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9583</v>
+        <v>9287</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13844</v>
+        <v>13824</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4261</v>
+        <v>-4537</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -668,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8657</v>
+        <v>8511</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13844</v>
+        <v>13824</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5187</v>
+        <v>-5313</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -713,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8847</v>
+        <v>8614</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13844</v>
+        <v>13824</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4997</v>
+        <v>-5210</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -758,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9144</v>
+        <v>9174</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13844</v>
+        <v>13824</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4700</v>
+        <v>-4650</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -785,6 +794,636 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-591</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6981</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>12824</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-5843</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-140</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>7116</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>12824</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-5708</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>7144</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>12824</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-5680</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-591</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>6984</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-9335</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-140</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>9117</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-7202</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>22-JUL-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>9174</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-7145</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-591</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>7247</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-9072</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>10498</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-5821</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-140</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>12161</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-4158</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>02-SEP-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>9597</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-6722</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>02-SEP-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-140</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>10809</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-5510</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>02-SEP-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>14092</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-2227</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>9089</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-7230</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>14092</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>16319</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-2227</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8511</v>
+        <v>7116</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13824</v>
+        <v>12838</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5313</v>
+        <v>-5722</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8614</v>
+        <v>8159</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13824</v>
+        <v>12838</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5210</v>
+        <v>-4679</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9174</v>
+        <v>8511</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13824</v>
+        <v>11837</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4650</v>
+        <v>-3326</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,26 +812,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6981</v>
+        <v>8807</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12824</v>
+        <v>11837</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5843</v>
+        <v>-3030</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>7116</v>
+        <v>8807</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12824</v>
+        <v>11837</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5708</v>
+        <v>-3030</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7144</v>
+        <v>7116</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12824</v>
+        <v>10837</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5680</v>
+        <v>-3721</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -947,26 +947,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6984</v>
+        <v>9117</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-9335</v>
+        <v>-7216</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -992,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9117</v>
+        <v>9174</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7202</v>
+        <v>-7159</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1037,26 +1037,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9174</v>
+        <v>9484</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-7145</v>
+        <v>-6849</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1086,13 +1086,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7247</v>
+        <v>7509</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-9072</v>
+        <v>-8824</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>20</v>
@@ -1134,10 +1134,10 @@
         <v>10498</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-5821</v>
+        <v>-5835</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1179,10 +1179,10 @@
         <v>12161</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4158</v>
+        <v>-4172</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1224,10 +1224,10 @@
         <v>9597</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6722</v>
+        <v>-6736</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10809</v>
+        <v>10823</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>-5510</v>
@@ -1314,10 +1314,10 @@
         <v>14092</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2227</v>
+        <v>-2241</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1359,10 +1359,10 @@
         <v>9089</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-7230</v>
+        <v>-7244</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1404,10 +1404,10 @@
         <v>14092</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16319</v>
+        <v>16333</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2227</v>
+        <v>-2241</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1424,6 +1424,141 @@
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-591</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>8617</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-7716</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>9089</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-7244</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>9484</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-6849</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7116</v>
+        <v>8511</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12838</v>
+        <v>13824</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5722</v>
+        <v>-5313</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -698,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,26 +722,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8159</v>
+        <v>8617</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12838</v>
+        <v>13824</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4679</v>
+        <v>-5207</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8511</v>
+        <v>9174</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11837</v>
+        <v>13824</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3326</v>
+        <v>-4650</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8807</v>
+        <v>8554</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11837</v>
+        <v>14825</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3030</v>
+        <v>-6271</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
         <v>8807</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11837</v>
+        <v>14825</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-3030</v>
+        <v>-6018</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>7116</v>
+        <v>9117</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10837</v>
+        <v>14825</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-3721</v>
+        <v>-5708</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -923,9 +923,9 @@
       <c r="I10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,30 +947,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9117</v>
+        <v>6982</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16333</v>
+        <v>12838</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-7216</v>
+        <v>-5856</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>10</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>9174</v>
+        <v>7116</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16333</v>
+        <v>12838</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7159</v>
+        <v>-5722</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,30 +1037,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>9484</v>
+        <v>8159</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16333</v>
+        <v>12838</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-6849</v>
+        <v>-4679</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1082,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>7509</v>
+        <v>8511</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16333</v>
+        <v>12838</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-8824</v>
+        <v>-4327</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,30 +1127,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>10498</v>
+        <v>8807</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16333</v>
+        <v>12838</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-5835</v>
+        <v>-4031</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12161</v>
+        <v>8807</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16333</v>
+        <v>12838</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4172</v>
+        <v>-4031</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9597</v>
+        <v>7116</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16333</v>
+        <v>10837</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6736</v>
+        <v>-3721</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1238,9 +1238,9 @@
       <c r="I17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,17 +1262,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10823</v>
+        <v>8117</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16333</v>
+        <v>11837</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5510</v>
+        <v>-3720</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>30</v>
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,26 +1307,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14092</v>
+        <v>8159</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16333</v>
+        <v>11837</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-2241</v>
+        <v>-3678</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9089</v>
+        <v>8159</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16333</v>
+        <v>11837</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-7244</v>
+        <v>-3678</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1373,9 +1373,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,30 +1397,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>14092</v>
+        <v>6982</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-2241</v>
+        <v>-9351</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>10</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,26 +1442,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8617</v>
+        <v>9117</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-7716</v>
+        <v>-7216</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9089</v>
+        <v>9174</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-7244</v>
+        <v>-7159</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>16-SEP-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,33 +1532,618 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9484</v>
+        <v>7062</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F24" s="2" t="n">
+        <v>-9271</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-142</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>12161</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-4172</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>26-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>12232</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-4101</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-591</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>7509</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-8824</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>10498</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-5835</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-140</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>12161</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-4172</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>02-SEP-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>9597</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-6736</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>02-SEP-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-140</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>10823</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-5510</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>02-SEP-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>14092</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-2241</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>9089</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-7244</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>09-SEP-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>14092</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-2241</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Air Arabia Egypt E5-591</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>8617</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-7716</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-105</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>9089</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-7244</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-633</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>9484</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F37" s="2" t="n">
         <v>-6849</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9117</v>
+        <v>8554</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13824</v>
+        <v>14825</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4707</v>
+        <v>-6271</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>9287</v>
+        <v>8807</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13824</v>
+        <v>14825</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4537</v>
+        <v>-6018</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -610,7 +610,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>31-MAY-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9287</v>
+        <v>9117</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13824</v>
+        <v>14825</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-4537</v>
+        <v>-5708</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -677,28 +677,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>8511</v>
+        <v>6979</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13824</v>
+        <v>12838</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5313</v>
+        <v>-5859</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -712,7 +712,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -722,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8617</v>
+        <v>7116</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>13824</v>
+        <v>12838</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5207</v>
+        <v>-5722</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>9174</v>
+        <v>8159</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13824</v>
+        <v>12838</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4650</v>
+        <v>-4679</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,7 +788,7 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8554</v>
+        <v>8511</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14825</v>
+        <v>12838</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6271</v>
+        <v>-4327</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -864,10 +864,10 @@
         <v>8807</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>14825</v>
+        <v>12838</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-6018</v>
+        <v>-4031</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>14-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9117</v>
+        <v>8807</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>14825</v>
+        <v>12838</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5708</v>
+        <v>-4031</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -925,7 +925,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,28 +947,28 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6982</v>
+        <v>8117</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>12838</v>
+        <v>11837</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-5856</v>
+        <v>-3720</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>7116</v>
+        <v>8159</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>12838</v>
+        <v>11837</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5722</v>
+        <v>-3678</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>8159</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12838</v>
+        <v>11837</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4679</v>
+        <v>-3678</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1058,7 +1058,7 @@
       <c r="I13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,30 +1082,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8511</v>
+        <v>6979</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12838</v>
+        <v>16333</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4327</v>
+        <v>-9354</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8807</v>
+        <v>9117</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12838</v>
+        <v>16333</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4031</v>
+        <v>-7216</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8807</v>
+        <v>9174</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12838</v>
+        <v>16333</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4031</v>
+        <v>-7159</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,30 +1217,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7116</v>
+        <v>7506</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>10837</v>
+        <v>16333</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3721</v>
+        <v>-8827</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8117</v>
+        <v>10498</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>11837</v>
+        <v>16333</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3720</v>
+        <v>-5835</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8159</v>
+        <v>12161</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>11837</v>
+        <v>16333</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3678</v>
+        <v>-4172</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>30</v>
@@ -1328,7 +1328,7 @@
       <c r="I19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8159</v>
+        <v>9597</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>11837</v>
+        <v>16333</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-3678</v>
+        <v>-6736</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,30 +1397,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>6982</v>
+        <v>10823</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-9351</v>
+        <v>-5510</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,30 +1442,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9117</v>
+        <v>14092</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-7216</v>
+        <v>-2241</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1491,13 +1491,13 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9174</v>
+        <v>9089</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-7159</v>
+        <v>-7244</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>30</v>
@@ -1508,7 +1508,7 @@
       <c r="I23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1522,7 +1522,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1532,30 +1532,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>7062</v>
+        <v>14092</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-9271</v>
+        <v>-2241</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,30 +1577,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>12161</v>
+        <v>8613</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-4172</v>
+        <v>-7720</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>12232</v>
+        <v>9089</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-4101</v>
+        <v>-7244</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>30</v>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1667,483 +1667,33 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>7509</v>
+        <v>9484</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>16333</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-8824</v>
+        <v>-6849</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>10498</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-5835</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>29-JUL-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-140</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>12161</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-4172</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>02-SEP-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>9597</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-6736</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>02-SEP-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-140</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>10823</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-5510</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>02-SEP-26</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>14092</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>-2241</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>9089</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>-7244</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n">
-        <v>14092</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>-2241</v>
-      </c>
-      <c r="G34" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-591</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n">
-        <v>8617</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>-7716</v>
-      </c>
-      <c r="G35" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>9089</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>-7244</v>
-      </c>
-      <c r="G36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n">
-        <v>9484</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>-6849</v>
-      </c>
-      <c r="G37" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -456,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -542,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8554</v>
+        <v>7078</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14825</v>
+        <v>13807</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6271</v>
+        <v>-6729</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>8807</v>
+        <v>7092</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>14825</v>
+        <v>13807</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6018</v>
+        <v>-6715</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -632,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>9117</v>
+        <v>7092</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>14825</v>
+        <v>13807</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-5708</v>
+        <v>-6715</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -677,26 +677,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6979</v>
+        <v>7078</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>12838</v>
+        <v>11811</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-5859</v>
+        <v>-4733</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -722,17 +722,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7116</v>
+        <v>7092</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12838</v>
+        <v>11811</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-5722</v>
+        <v>-4719</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -743,9 +743,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -771,13 +771,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8159</v>
+        <v>6017</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12838</v>
+        <v>11811</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-4679</v>
+        <v>-5794</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -788,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-115</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8511</v>
+        <v>6017</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12838</v>
+        <v>11811</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-4327</v>
+        <v>-5794</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -833,9 +833,9 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>21-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-142</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8807</v>
+        <v>6087</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12838</v>
+        <v>11811</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-4031</v>
+        <v>-5724</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -878,9 +878,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>14-JUN-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,26 +902,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8807</v>
+        <v>10052</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12838</v>
+        <v>10806</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-4031</v>
+        <v>-754</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8117</v>
+        <v>12146</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11837</v>
+        <v>16321</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-3720</v>
+        <v>-4175</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -982,7 +982,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8159</v>
+        <v>12216</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>11837</v>
+        <v>16321</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-3678</v>
+        <v>-4105</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1027,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>26-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8159</v>
+        <v>12216</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>11837</v>
+        <v>16321</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3678</v>
+        <v>-4105</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>30</v>
@@ -1072,7 +1072,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1082,26 +1082,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6979</v>
+        <v>10945</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-9354</v>
+        <v>-5376</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9117</v>
+        <v>12146</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-7216</v>
+        <v>-4175</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1148,9 +1148,9 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9174</v>
+        <v>12216</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-7159</v>
+        <v>-4105</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1193,9 +1193,9 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1217,26 +1217,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-591</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7506</v>
+        <v>9549</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-8827</v>
+        <v>-6772</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1262,30 +1262,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10498</v>
+        <v>10792</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5835</v>
+        <v>-5529</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,26 +1307,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>12161</v>
+        <v>14561</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-4172</v>
+        <v>-1760</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1356,13 +1356,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9597</v>
+        <v>9047</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-6736</v>
+        <v>-7274</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1387,7 +1387,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1397,26 +1397,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10823</v>
+        <v>14561</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-5510</v>
+        <v>-1760</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1442,30 +1442,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>14092</v>
+        <v>9047</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-2241</v>
+        <v>-7274</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09-SEP-26</t>
+          <t>16-SEP-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1487,213 +1487,33 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9089</v>
+        <v>9926</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>16333</v>
+        <v>16321</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-7244</v>
+        <v>-6395</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>09-SEP-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>14092</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-2241</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Air Arabia Egypt E5-591</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>8613</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-7720</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-105</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>9089</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-7244</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>16-SEP-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-435</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-633</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>9484</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>16333</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-6849</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_HMB_ELQ_threats.xlsx
+++ b/excel_routes/route_HMB_ELQ_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -48,14 +48,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF3CD"/>
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,12 +465,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -546,13 +555,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>7078</v>
+        <v>8404</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>13807</v>
+        <v>11702</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-6729</v>
+        <v>-3298</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -565,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7092</v>
+        <v>7010</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13807</v>
+        <v>11702</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-6715</v>
+        <v>-4692</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -610,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -622,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -632,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7092</v>
+        <v>8004</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13807</v>
+        <v>11702</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6715</v>
+        <v>-3698</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -655,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -667,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -681,13 +690,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>7078</v>
+        <v>5451</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11811</v>
+        <v>11702</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4733</v>
+        <v>-6251</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -700,7 +709,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -712,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -726,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7092</v>
+        <v>5947</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11811</v>
+        <v>11702</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4719</v>
+        <v>-5755</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -745,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6017</v>
+        <v>5402</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11811</v>
+        <v>9715</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-5794</v>
+        <v>-4313</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -802,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -812,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6017</v>
+        <v>5451</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11811</v>
+        <v>9715</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-5794</v>
+        <v>-4264</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -835,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -847,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>21-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -857,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6087</v>
+        <v>5947</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11811</v>
+        <v>9715</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-5724</v>
+        <v>-3768</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -880,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -892,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -902,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10052</v>
+        <v>6850</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10806</v>
+        <v>16174</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-754</v>
+        <v>-9324</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -937,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -947,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-142</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>12146</v>
+        <v>8004</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-4175</v>
+        <v>-8170</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -970,7 +979,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -982,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -996,13 +1005,13 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>12216</v>
+        <v>8004</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-4105</v>
+        <v>-8170</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1015,7 +1024,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1027,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1037,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-115</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>12216</v>
+        <v>8606</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4105</v>
+        <v>-7568</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1086,13 +1095,13 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>10945</v>
+        <v>9715</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-5376</v>
+        <v>-6459</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1103,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1131,13 +1140,13 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12146</v>
+        <v>12033</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-4175</v>
+        <v>-4141</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>30</v>
@@ -1148,7 +1157,7 @@
       <c r="I15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1162,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>02-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1176,13 +1185,13 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>12216</v>
+        <v>9467</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4105</v>
+        <v>-6707</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1195,7 +1204,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1217,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>9549</v>
+        <v>10695</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-6772</v>
+        <v>-5479</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>30</v>
@@ -1240,7 +1249,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1262,28 +1271,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-140</t>
+          <t>EgyptAir MS-633</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>10792</v>
+        <v>13883</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5529</v>
+        <v>-2291</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1297,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>02-SEP-26</t>
+          <t>09-SEP-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1307,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>14561</v>
+        <v>8942</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-1760</v>
+        <v>-7232</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1352,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Nesma Airlines NE-140</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9047</v>
+        <v>8997</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-7274</v>
+        <v>-7177</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>30</v>
@@ -1373,7 +1382,7 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1401,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>14561</v>
+        <v>13883</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-1760</v>
+        <v>-2291</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1418,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1442,28 +1451,28 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-105</t>
+          <t>Air Arabia Egypt E5-591</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9047</v>
+        <v>8451</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-7274</v>
+        <v>-7723</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1487,33 +1496,78 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-633</t>
+          <t>Nile Air NP-105</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9926</v>
+        <v>8942</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>16321</v>
+        <v>16174</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-6395</v>
+        <v>-7232</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>16-SEP-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-435</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-140</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>8997</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>16174</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-7177</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
